--- a/premise/data/additional_inventories/lci-PV-perovskite.xlsx
+++ b/premise/data/additional_inventories/lci-PV-perovskite.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10811"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/romain/GitHub/premise/premise/data/additional_inventories/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C690D11-DE9C-5D4F-8BCF-4C186FDF7B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2BAE77C-38CC-B748-90A0-DBA3BF4E3CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4440" yWindow="760" windowWidth="25800" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PV-perovskite" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2864" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2864" uniqueCount="459">
   <si>
     <t>Database</t>
   </si>
@@ -849,6 +849,9 @@
   </si>
   <si>
     <t>market for water, deionised</t>
+  </si>
+  <si>
+    <t>Methanol</t>
   </si>
   <si>
     <t>methylamine</t>
@@ -1770,6 +1773,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:L747"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1791,7 +1795,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1799,7 +1804,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>135</v>
       </c>
@@ -1807,7 +1812,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1815,7 +1820,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1823,7 +1828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1831,7 +1836,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1839,7 +1844,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1847,7 +1852,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -1859,7 +1864,7 @@
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -1885,7 +1890,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="str">
         <f>B3</f>
         <v>perovskite wafer production</v>
@@ -1909,7 +1914,7 @@
         <v>perovskite wafer</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -1930,9 +1935,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B14" s="4">
         <f>1830.1110288/35467268</f>
@@ -1948,10 +1953,10 @@
         <v>77</v>
       </c>
       <c r="G14" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -1972,7 +1977,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -1993,7 +1998,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -2014,7 +2019,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>51</v>
       </c>
@@ -2038,7 +2043,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -2059,7 +2064,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>55</v>
       </c>
@@ -2083,7 +2088,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -2104,7 +2109,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -2125,7 +2130,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -2146,7 +2151,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -2167,7 +2172,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -2188,7 +2193,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -2212,7 +2217,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -2233,7 +2238,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -2254,7 +2259,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>29</v>
       </c>
@@ -2275,9 +2280,9 @@
         <v>127</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B30" s="3">
         <f>59478608.436/35467268</f>
@@ -2293,10 +2298,10 @@
         <v>77</v>
       </c>
       <c r="G30" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -2317,7 +2322,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>60</v>
       </c>
@@ -2335,7 +2340,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>63</v>
       </c>
@@ -2353,7 +2358,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>64</v>
       </c>
@@ -2371,7 +2376,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>65</v>
       </c>
@@ -2389,7 +2394,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>66</v>
       </c>
@@ -2407,7 +2412,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>68</v>
       </c>
@@ -2425,7 +2430,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>69</v>
       </c>
@@ -2443,7 +2448,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>70</v>
       </c>
@@ -2461,7 +2466,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>71</v>
       </c>
@@ -2479,7 +2484,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>72</v>
       </c>
@@ -2497,7 +2502,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>73</v>
       </c>
@@ -2515,7 +2520,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>74</v>
       </c>
@@ -2533,7 +2538,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>75</v>
       </c>
@@ -2551,7 +2556,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>76</v>
       </c>
@@ -2569,7 +2574,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>76</v>
       </c>
@@ -2587,7 +2592,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="49" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>1</v>
       </c>
@@ -2595,7 +2602,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
         <v>135</v>
       </c>
@@ -2603,7 +2610,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>3</v>
       </c>
@@ -2611,7 +2618,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>5</v>
       </c>
@@ -2619,7 +2626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>6</v>
       </c>
@@ -2627,7 +2634,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>7</v>
       </c>
@@ -2635,7 +2642,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>8</v>
       </c>
@@ -2643,7 +2650,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>9</v>
       </c>
@@ -2655,7 +2662,7 @@
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>10</v>
       </c>
@@ -2681,7 +2688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" t="str">
         <f>B49</f>
         <v>perovskite wafer packaging</v>
@@ -2705,7 +2712,7 @@
         <v>perovskite wafer, packaged</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>84</v>
       </c>
@@ -2726,7 +2733,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>85</v>
       </c>
@@ -2747,7 +2754,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>86</v>
       </c>
@@ -2768,7 +2775,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>45</v>
       </c>
@@ -2788,7 +2795,9 @@
         <v>44</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="65" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>1</v>
       </c>
@@ -2796,7 +2805,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
         <v>135</v>
       </c>
@@ -2804,7 +2813,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>3</v>
       </c>
@@ -2812,7 +2821,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>5</v>
       </c>
@@ -2820,7 +2829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>6</v>
       </c>
@@ -2828,7 +2837,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>7</v>
       </c>
@@ -2836,7 +2845,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>8</v>
       </c>
@@ -2844,7 +2853,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>9</v>
       </c>
@@ -2856,7 +2865,7 @@
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>10</v>
       </c>
@@ -2882,7 +2891,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" t="str">
         <f>B65</f>
         <v>perovskite wafer transport</v>
@@ -2906,7 +2915,7 @@
         <v>perovskite wafer, transported</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>93</v>
       </c>
@@ -2927,7 +2936,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>94</v>
       </c>
@@ -2948,9 +2957,9 @@
         <v>156</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B77">
         <f>428058757.128493/35422933.915</f>
@@ -2966,10 +2975,10 @@
         <v>77</v>
       </c>
       <c r="G77" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>95</v>
       </c>
@@ -2990,7 +2999,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>82</v>
       </c>
@@ -3011,7 +3020,9 @@
         <v>83</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="82" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>1</v>
       </c>
@@ -3019,7 +3030,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
         <v>135</v>
       </c>
@@ -3027,7 +3038,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>3</v>
       </c>
@@ -3035,7 +3046,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>5</v>
       </c>
@@ -3043,7 +3054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>6</v>
       </c>
@@ -3051,7 +3062,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>7</v>
       </c>
@@ -3059,7 +3070,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>8</v>
       </c>
@@ -3067,7 +3078,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>9</v>
       </c>
@@ -3079,7 +3090,7 @@
       <c r="G89" s="1"/>
       <c r="H89" s="1"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>10</v>
       </c>
@@ -3105,7 +3116,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" t="str">
         <f>B82</f>
         <v>perovskite wafer cleaning</v>
@@ -3129,7 +3140,7 @@
         <v>perovskite wafer, cleaned</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>90</v>
       </c>
@@ -3149,7 +3160,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>99</v>
       </c>
@@ -3170,7 +3181,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>100</v>
       </c>
@@ -3191,7 +3202,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>104</v>
       </c>
@@ -3215,7 +3226,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>100</v>
       </c>
@@ -3236,7 +3247,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>106</v>
       </c>
@@ -3257,7 +3268,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>100</v>
       </c>
@@ -3278,7 +3289,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>100</v>
       </c>
@@ -3299,7 +3310,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>108</v>
       </c>
@@ -3320,7 +3331,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>25</v>
       </c>
@@ -3344,7 +3355,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>115</v>
       </c>
@@ -3365,10 +3376,10 @@
         <v>116</v>
       </c>
       <c r="H102" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>117</v>
       </c>
@@ -3389,10 +3400,10 @@
         <v>118</v>
       </c>
       <c r="H103" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>51</v>
       </c>
@@ -3416,7 +3427,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>113</v>
       </c>
@@ -3440,7 +3451,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>114</v>
       </c>
@@ -3464,7 +3475,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>122</v>
       </c>
@@ -3485,7 +3496,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>84</v>
       </c>
@@ -3506,9 +3517,9 @@
         <v>124</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B109">
         <f>-3000/35367093.098703</f>
@@ -3527,9 +3538,9 @@
         <v>125</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B110">
         <f>-5000/35367093.098703</f>
@@ -3548,7 +3559,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>95</v>
       </c>
@@ -3569,7 +3580,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>130</v>
       </c>
@@ -3593,9 +3604,9 @@
         <v>129</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B113">
         <f>-43830000/35367093.098703</f>
@@ -3611,15 +3622,15 @@
         <v>77</v>
       </c>
       <c r="G113" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H113" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B114">
         <f>-65745000/35367093.098703</f>
@@ -3635,15 +3646,15 @@
         <v>77</v>
       </c>
       <c r="G114" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H114" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B115">
         <f>-66621600/35367093.098703</f>
@@ -3659,13 +3670,13 @@
         <v>77</v>
       </c>
       <c r="G115" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H115" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>132</v>
       </c>
@@ -3689,7 +3700,9 @@
         <v>212</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="119" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
         <v>1</v>
       </c>
@@ -3697,7 +3710,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="s">
         <v>2</v>
       </c>
@@ -3705,7 +3718,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>3</v>
       </c>
@@ -3713,7 +3726,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>5</v>
       </c>
@@ -3721,7 +3734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>6</v>
       </c>
@@ -3729,7 +3742,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>7</v>
       </c>
@@ -3737,7 +3750,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>8</v>
       </c>
@@ -3745,7 +3758,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
         <v>9</v>
       </c>
@@ -3757,7 +3770,7 @@
       <c r="G126" s="1"/>
       <c r="H126" s="1"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
         <v>10</v>
       </c>
@@ -3783,7 +3796,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" t="str">
         <f>B119</f>
         <v>PECVD of thin film layer, for perovskite</v>
@@ -3806,7 +3819,7 @@
         <v>cell, perovskite, to sputter</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>144</v>
       </c>
@@ -3827,10 +3840,10 @@
         <v>143</v>
       </c>
       <c r="H129" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>97</v>
       </c>
@@ -3851,7 +3864,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>145</v>
       </c>
@@ -3872,10 +3885,10 @@
         <v>146</v>
       </c>
       <c r="H131" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>117</v>
       </c>
@@ -3896,10 +3909,10 @@
         <v>118</v>
       </c>
       <c r="H132" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>51</v>
       </c>
@@ -3923,7 +3936,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>147</v>
       </c>
@@ -3944,9 +3957,9 @@
         <v>56</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B135">
         <f>46.5001236/35317005.6480545</f>
@@ -3962,13 +3975,13 @@
         <v>77</v>
       </c>
       <c r="G135" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H135" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>148</v>
       </c>
@@ -3989,7 +4002,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>117</v>
       </c>
@@ -4031,7 +4044,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>150</v>
       </c>
@@ -4052,7 +4065,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>151</v>
       </c>
@@ -4073,7 +4086,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>94</v>
       </c>
@@ -4094,7 +4107,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>93</v>
       </c>
@@ -4115,7 +4128,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>60</v>
       </c>
@@ -4136,7 +4149,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>63</v>
       </c>
@@ -4157,7 +4170,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>64</v>
       </c>
@@ -4178,7 +4191,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>184</v>
       </c>
@@ -4199,7 +4212,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>66</v>
       </c>
@@ -4220,7 +4233,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>65</v>
       </c>
@@ -4241,7 +4254,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>68</v>
       </c>
@@ -4262,7 +4275,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>69</v>
       </c>
@@ -4283,7 +4296,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>185</v>
       </c>
@@ -4304,7 +4317,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>186</v>
       </c>
@@ -4325,7 +4338,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>70</v>
       </c>
@@ -4346,7 +4359,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>71</v>
       </c>
@@ -4367,7 +4380,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>72</v>
       </c>
@@ -4388,7 +4401,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>73</v>
       </c>
@@ -4409,7 +4422,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>74</v>
       </c>
@@ -4430,7 +4443,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>187</v>
       </c>
@@ -4451,7 +4464,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>188</v>
       </c>
@@ -4472,7 +4485,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>189</v>
       </c>
@@ -4493,7 +4506,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>75</v>
       </c>
@@ -4514,7 +4527,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>190</v>
       </c>
@@ -4535,7 +4548,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>191</v>
       </c>
@@ -4556,9 +4569,9 @@
         <v>178</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B164">
         <f>30.6056124/35317005.6480545</f>
@@ -4574,10 +4587,10 @@
         <v>77</v>
       </c>
       <c r="G164" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>179</v>
       </c>
@@ -4598,7 +4611,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>51</v>
       </c>
@@ -4622,7 +4635,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>180</v>
       </c>
@@ -4643,7 +4656,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>147</v>
       </c>
@@ -4664,7 +4677,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>94</v>
       </c>
@@ -4685,7 +4698,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>93</v>
       </c>
@@ -4706,7 +4719,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>194</v>
       </c>
@@ -4727,7 +4740,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>58</v>
       </c>
@@ -4751,7 +4764,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>58</v>
       </c>
@@ -4775,7 +4788,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>192</v>
       </c>
@@ -4796,7 +4809,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>193</v>
       </c>
@@ -4817,7 +4830,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>190</v>
       </c>
@@ -4838,7 +4851,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>196</v>
       </c>
@@ -4862,9 +4875,9 @@
         <v>202</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B178">
         <f>312.42024*0.08988/35317005.6480545</f>
@@ -4880,13 +4893,13 @@
         <v>77</v>
       </c>
       <c r="G178" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H178" s="6" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>197</v>
       </c>
@@ -4910,9 +4923,9 @@
         <v>205</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B180">
         <f>5259600*0.07078/35317005.6480545</f>
@@ -4928,13 +4941,13 @@
         <v>77</v>
       </c>
       <c r="G180" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H180" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>51</v>
       </c>
@@ -4955,7 +4968,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>206</v>
       </c>
@@ -4979,7 +4992,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>51</v>
       </c>
@@ -5000,7 +5013,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>114</v>
       </c>
@@ -5024,7 +5037,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>95</v>
       </c>
@@ -5045,7 +5058,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>130</v>
       </c>
@@ -5066,7 +5079,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>206</v>
       </c>
@@ -5090,9 +5103,9 @@
         <v>207</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B188">
         <f>-(20161800+157788)/35317005.6480545</f>
@@ -5108,15 +5121,15 @@
         <v>77</v>
       </c>
       <c r="G188" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H188" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="189" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" s="5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B189">
         <f>-(157788)/35317005.6480545</f>
@@ -5132,10 +5145,12 @@
         <v>77</v>
       </c>
       <c r="G189" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="192" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="192" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" s="2" t="s">
         <v>1</v>
       </c>
@@ -5143,7 +5158,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" s="5" t="s">
         <v>2</v>
       </c>
@@ -5151,7 +5166,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>3</v>
       </c>
@@ -5159,7 +5174,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>5</v>
       </c>
@@ -5167,7 +5182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>6</v>
       </c>
@@ -5175,7 +5190,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>7</v>
       </c>
@@ -5183,7 +5198,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>8</v>
       </c>
@@ -5191,7 +5206,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" s="1" t="s">
         <v>9</v>
       </c>
@@ -5202,7 +5217,7 @@
       <c r="F199" s="1"/>
       <c r="G199" s="1"/>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" s="1" t="s">
         <v>10</v>
       </c>
@@ -5228,7 +5243,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" t="str">
         <f>B192</f>
         <v>sputter process 1, perovskite cell</v>
@@ -5252,7 +5267,7 @@
         <v>perovskite cell, sputtered 1</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>141</v>
       </c>
@@ -5273,7 +5288,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>217</v>
       </c>
@@ -5294,7 +5309,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>115</v>
       </c>
@@ -5315,10 +5330,10 @@
         <v>116</v>
       </c>
       <c r="H204" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>145</v>
       </c>
@@ -5339,10 +5354,10 @@
         <v>146</v>
       </c>
       <c r="H205" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>117</v>
       </c>
@@ -5363,10 +5378,10 @@
         <v>118</v>
       </c>
       <c r="H206" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>51</v>
       </c>
@@ -5387,7 +5402,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>206</v>
       </c>
@@ -5411,7 +5426,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>114</v>
       </c>
@@ -5432,7 +5447,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>95</v>
       </c>
@@ -5453,7 +5468,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>130</v>
       </c>
@@ -5474,7 +5489,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>206</v>
       </c>
@@ -5498,9 +5513,9 @@
         <v>207</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B213">
         <f>-1472688/35266918.197406</f>
@@ -5516,13 +5531,15 @@
         <v>77</v>
       </c>
       <c r="G213" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H213" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="216" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="215" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="216" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216" s="2" t="s">
         <v>1</v>
       </c>
@@ -5530,7 +5547,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="217" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217" s="5" t="s">
         <v>2</v>
       </c>
@@ -5538,7 +5555,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>3</v>
       </c>
@@ -5546,7 +5563,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>5</v>
       </c>
@@ -5554,7 +5571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>6</v>
       </c>
@@ -5562,7 +5579,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>7</v>
       </c>
@@ -5570,7 +5587,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>8</v>
       </c>
@@ -5578,7 +5595,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223" s="1" t="s">
         <v>9</v>
       </c>
@@ -5589,7 +5606,7 @@
       <c r="F223" s="1"/>
       <c r="G223" s="1"/>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224" s="1" t="s">
         <v>10</v>
       </c>
@@ -5615,7 +5632,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A225" t="str">
         <f>B216</f>
         <v>sputter process 2, perovskite cell</v>
@@ -5639,7 +5656,7 @@
         <v>perovskite cell, sputtered 2</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>215</v>
       </c>
@@ -5660,7 +5677,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>217</v>
       </c>
@@ -5681,7 +5698,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>115</v>
       </c>
@@ -5702,10 +5719,10 @@
         <v>116</v>
       </c>
       <c r="H228" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>145</v>
       </c>
@@ -5726,10 +5743,10 @@
         <v>146</v>
       </c>
       <c r="H229" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>117</v>
       </c>
@@ -5750,10 +5767,10 @@
         <v>118</v>
       </c>
       <c r="H230" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>51</v>
       </c>
@@ -5774,7 +5791,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>206</v>
       </c>
@@ -5798,7 +5815,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>114</v>
       </c>
@@ -5819,7 +5836,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>95</v>
       </c>
@@ -5840,7 +5857,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>130</v>
       </c>
@@ -5861,7 +5878,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>206</v>
       </c>
@@ -5885,9 +5902,9 @@
         <v>207</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B237">
         <f>-1472688/35266918.197406</f>
@@ -5903,13 +5920,15 @@
         <v>77</v>
       </c>
       <c r="G237" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H237" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="240" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="239" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="240" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A240" s="2" t="s">
         <v>1</v>
       </c>
@@ -5917,7 +5936,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="241" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A241" s="5" t="s">
         <v>2</v>
       </c>
@@ -5925,7 +5944,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>3</v>
       </c>
@@ -5933,7 +5952,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>5</v>
       </c>
@@ -5941,7 +5960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>6</v>
       </c>
@@ -5949,7 +5968,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>7</v>
       </c>
@@ -5957,7 +5976,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>8</v>
       </c>
@@ -5965,7 +5984,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A247" s="1" t="s">
         <v>9</v>
       </c>
@@ -5976,7 +5995,7 @@
       <c r="F247" s="1"/>
       <c r="G247" s="1"/>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A248" s="1" t="s">
         <v>10</v>
       </c>
@@ -6002,7 +6021,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A249" t="str">
         <f>B240</f>
         <v>spiro-OMeTAD deposition of perovskite cell</v>
@@ -6026,7 +6045,7 @@
         <v>spiro-OMeTAD deposited perovskite cell</v>
       </c>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>219</v>
       </c>
@@ -6047,7 +6066,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>17</v>
       </c>
@@ -6068,7 +6087,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>226</v>
       </c>
@@ -6086,10 +6105,10 @@
         <v>77</v>
       </c>
       <c r="G252" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.2">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>115</v>
       </c>
@@ -6110,7 +6129,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>227</v>
       </c>
@@ -6128,10 +6147,10 @@
         <v>77</v>
       </c>
       <c r="G254" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.2">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>228</v>
       </c>
@@ -6149,10 +6168,10 @@
         <v>77</v>
       </c>
       <c r="G255" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.2">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>229</v>
       </c>
@@ -6170,10 +6189,10 @@
         <v>77</v>
       </c>
       <c r="G256" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>230</v>
       </c>
@@ -6191,10 +6210,10 @@
         <v>77</v>
       </c>
       <c r="G257" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>231</v>
       </c>
@@ -6212,10 +6231,10 @@
         <v>77</v>
       </c>
       <c r="G258" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>17</v>
       </c>
@@ -6236,9 +6255,9 @@
         <v>225</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B260">
         <f>575.256965526288/35166743.2961089</f>
@@ -6254,10 +6273,10 @@
         <v>77</v>
       </c>
       <c r="G260" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>228</v>
       </c>
@@ -6275,10 +6294,10 @@
         <v>77</v>
       </c>
       <c r="G261" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>232</v>
       </c>
@@ -6296,10 +6315,10 @@
         <v>77</v>
       </c>
       <c r="G262" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>233</v>
       </c>
@@ -6317,10 +6336,10 @@
         <v>77</v>
       </c>
       <c r="G263" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>104</v>
       </c>
@@ -6341,9 +6360,9 @@
         <v>105</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B265">
         <f>2.87174093374893/35166743.2961089</f>
@@ -6359,10 +6378,10 @@
         <v>77</v>
       </c>
       <c r="G265" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>234</v>
       </c>
@@ -6380,10 +6399,10 @@
         <v>77</v>
       </c>
       <c r="G266" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>100</v>
       </c>
@@ -6404,7 +6423,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>235</v>
       </c>
@@ -6422,10 +6441,10 @@
         <v>77</v>
       </c>
       <c r="G268" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>228</v>
       </c>
@@ -6443,10 +6462,10 @@
         <v>77</v>
       </c>
       <c r="G269" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>236</v>
       </c>
@@ -6464,10 +6483,10 @@
         <v>77</v>
       </c>
       <c r="G270" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>235</v>
       </c>
@@ -6485,10 +6504,10 @@
         <v>77</v>
       </c>
       <c r="G271" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>236</v>
       </c>
@@ -6506,10 +6525,10 @@
         <v>77</v>
       </c>
       <c r="G272" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>237</v>
       </c>
@@ -6527,10 +6546,10 @@
         <v>77</v>
       </c>
       <c r="G273" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>108</v>
       </c>
@@ -6551,7 +6570,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>238</v>
       </c>
@@ -6569,10 +6588,10 @@
         <v>77</v>
       </c>
       <c r="G275" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>25</v>
       </c>
@@ -6593,7 +6612,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>239</v>
       </c>
@@ -6611,10 +6630,10 @@
         <v>77</v>
       </c>
       <c r="G277" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>100</v>
       </c>
@@ -6635,7 +6654,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>240</v>
       </c>
@@ -6653,10 +6672,10 @@
         <v>77</v>
       </c>
       <c r="G279" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>238</v>
       </c>
@@ -6674,10 +6693,10 @@
         <v>77</v>
       </c>
       <c r="G280" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>241</v>
       </c>
@@ -6695,10 +6714,10 @@
         <v>77</v>
       </c>
       <c r="G281" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>242</v>
       </c>
@@ -6716,10 +6735,10 @@
         <v>77</v>
       </c>
       <c r="G282" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>117</v>
       </c>
@@ -6740,7 +6759,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>104</v>
       </c>
@@ -6761,7 +6780,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>243</v>
       </c>
@@ -6773,16 +6792,16 @@
         <v>79</v>
       </c>
       <c r="E285" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F285" t="s">
         <v>77</v>
       </c>
       <c r="G285" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>244</v>
       </c>
@@ -6800,10 +6819,10 @@
         <v>77</v>
       </c>
       <c r="G286" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>17</v>
       </c>
@@ -6824,7 +6843,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>25</v>
       </c>
@@ -6845,7 +6864,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>245</v>
       </c>
@@ -6866,7 +6885,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>246</v>
       </c>
@@ -6884,10 +6903,10 @@
         <v>77</v>
       </c>
       <c r="G290" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.2">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>247</v>
       </c>
@@ -6905,10 +6924,10 @@
         <v>77</v>
       </c>
       <c r="G291" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.2">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>248</v>
       </c>
@@ -6926,10 +6945,10 @@
         <v>77</v>
       </c>
       <c r="G292" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.2">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>245</v>
       </c>
@@ -6950,7 +6969,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>249</v>
       </c>
@@ -6968,12 +6987,12 @@
         <v>77</v>
       </c>
       <c r="G294" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.2">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B295">
         <f>2381.0003944374/35166743.2961089</f>
@@ -6989,10 +7008,10 @@
         <v>77</v>
       </c>
       <c r="G295" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.2">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>250</v>
       </c>
@@ -7010,12 +7029,12 @@
         <v>77</v>
       </c>
       <c r="G296" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.2">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B297">
         <f>-127.229028710395/35166743.2961089</f>
@@ -7031,10 +7050,10 @@
         <v>77</v>
       </c>
       <c r="G297" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.2">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>197</v>
       </c>
@@ -7055,9 +7074,9 @@
         <v>201</v>
       </c>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B299">
         <f>413.494343308785/35166743.2961089</f>
@@ -7073,10 +7092,10 @@
         <v>77</v>
       </c>
       <c r="G299" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.2">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>256</v>
       </c>
@@ -7097,7 +7116,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>252</v>
       </c>
@@ -7118,7 +7137,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>254</v>
       </c>
@@ -7139,7 +7158,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>238</v>
       </c>
@@ -7157,10 +7176,10 @@
         <v>77</v>
       </c>
       <c r="G303" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.2">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>241</v>
       </c>
@@ -7178,10 +7197,10 @@
         <v>77</v>
       </c>
       <c r="G304" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.2">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>117</v>
       </c>
@@ -7202,7 +7221,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>246</v>
       </c>
@@ -7220,10 +7239,10 @@
         <v>77</v>
       </c>
       <c r="G306" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.2">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>247</v>
       </c>
@@ -7241,10 +7260,10 @@
         <v>77</v>
       </c>
       <c r="G307" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.2">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>249</v>
       </c>
@@ -7262,10 +7281,10 @@
         <v>77</v>
       </c>
       <c r="G308" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.2">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>250</v>
       </c>
@@ -7283,12 +7302,12 @@
         <v>77</v>
       </c>
       <c r="G309" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.2">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B310">
         <f>-127.960230024823/35166743.2961089</f>
@@ -7304,10 +7323,10 @@
         <v>77</v>
       </c>
       <c r="G310" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.2">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>197</v>
       </c>
@@ -7328,9 +7347,9 @@
         <v>201</v>
       </c>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B312">
         <f>415.870747580675/35166743.2961089</f>
@@ -7346,10 +7365,10 @@
         <v>77</v>
       </c>
       <c r="G312" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.2">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>256</v>
       </c>
@@ -7367,7 +7386,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>254</v>
       </c>
@@ -7388,7 +7407,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>117</v>
       </c>
@@ -7412,7 +7431,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>206</v>
       </c>
@@ -7436,7 +7455,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>51</v>
       </c>
@@ -7457,7 +7476,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>114</v>
       </c>
@@ -7481,7 +7500,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>95</v>
       </c>
@@ -7502,7 +7521,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>130</v>
       </c>
@@ -7523,9 +7542,9 @@
         <v>131</v>
       </c>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B321">
         <f>-14025600/35166743.2961089</f>
@@ -7541,13 +7560,13 @@
         <v>77</v>
       </c>
       <c r="G321" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H321" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>206</v>
       </c>
@@ -7571,7 +7590,9 @@
         <v>207</v>
       </c>
     </row>
-    <row r="325" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="324" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="325" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A325" s="2" t="s">
         <v>1</v>
       </c>
@@ -7579,7 +7600,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="326" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A326" s="5" t="s">
         <v>2</v>
       </c>
@@ -7587,7 +7608,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>3</v>
       </c>
@@ -7595,7 +7616,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>5</v>
       </c>
@@ -7603,7 +7624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>6</v>
       </c>
@@ -7611,7 +7632,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>7</v>
       </c>
@@ -7619,7 +7640,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>8</v>
       </c>
@@ -7627,7 +7648,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A332" s="1" t="s">
         <v>9</v>
       </c>
@@ -7638,7 +7659,7 @@
       <c r="F332" s="1"/>
       <c r="G332" s="1"/>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A333" s="1" t="s">
         <v>10</v>
       </c>
@@ -7664,7 +7685,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A334" t="str">
         <f>B325</f>
         <v>perovskite cell deposition</v>
@@ -7688,7 +7709,7 @@
         <v>deposited perovskite cell</v>
       </c>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>223</v>
       </c>
@@ -7709,7 +7730,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>51</v>
       </c>
@@ -7730,9 +7751,9 @@
         <v>52</v>
       </c>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B337">
         <f>4.17324674571931/35116655.8454604</f>
@@ -7748,13 +7769,13 @@
         <v>77</v>
       </c>
       <c r="G337" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H337" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.2">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>266</v>
       </c>
@@ -7775,7 +7796,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>260</v>
       </c>
@@ -7796,7 +7817,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>117</v>
       </c>
@@ -7820,7 +7841,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>261</v>
       </c>
@@ -7841,7 +7862,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>269</v>
       </c>
@@ -7862,7 +7883,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>252</v>
       </c>
@@ -7883,7 +7904,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>242</v>
       </c>
@@ -7901,10 +7922,10 @@
         <v>77</v>
       </c>
       <c r="G344" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.2">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>262</v>
       </c>
@@ -7922,10 +7943,10 @@
         <v>77</v>
       </c>
       <c r="G345" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>252</v>
       </c>
@@ -7946,7 +7967,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>266</v>
       </c>
@@ -7967,7 +7988,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>266</v>
       </c>
@@ -7988,7 +8009,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>263</v>
       </c>
@@ -8006,10 +8027,10 @@
         <v>77</v>
       </c>
       <c r="G349" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.2">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>264</v>
       </c>
@@ -8021,16 +8042,16 @@
         <v>79</v>
       </c>
       <c r="E350" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F350" t="s">
         <v>77</v>
       </c>
       <c r="G350" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.2">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>261</v>
       </c>
@@ -8051,7 +8072,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>252</v>
       </c>
@@ -8072,7 +8093,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
         <v>266</v>
       </c>
@@ -8093,7 +8114,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
         <v>260</v>
       </c>
@@ -8114,7 +8135,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
         <v>106</v>
       </c>
@@ -8135,7 +8156,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>261</v>
       </c>
@@ -8156,7 +8177,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>252</v>
       </c>
@@ -8177,7 +8198,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>261</v>
       </c>
@@ -8198,7 +8219,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>266</v>
       </c>
@@ -8219,7 +8240,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
         <v>114</v>
       </c>
@@ -8243,7 +8264,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>95</v>
       </c>
@@ -8264,7 +8285,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>130</v>
       </c>
@@ -8285,9 +8306,9 @@
         <v>131</v>
       </c>
     </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B363">
         <f>-(16594290.8653846+438300)/35116655.8454604</f>
@@ -8303,13 +8324,13 @@
         <v>77</v>
       </c>
       <c r="G363" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H363" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>206</v>
       </c>
@@ -8333,7 +8354,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>206</v>
       </c>
@@ -8357,23 +8378,25 @@
         <v>207</v>
       </c>
     </row>
-    <row r="368" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="367" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="368" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A368" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="369" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A369" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B369" s="5" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
         <v>3</v>
       </c>
@@ -8381,7 +8404,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
         <v>5</v>
       </c>
@@ -8389,15 +8412,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
         <v>6</v>
       </c>
       <c r="B372" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.2">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
         <v>7</v>
       </c>
@@ -8405,7 +8428,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
         <v>8</v>
       </c>
@@ -8413,7 +8436,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A375" s="1" t="s">
         <v>9</v>
       </c>
@@ -8424,7 +8447,7 @@
       <c r="F375" s="1"/>
       <c r="G375" s="1"/>
     </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A376" s="1" t="s">
         <v>10</v>
       </c>
@@ -8450,7 +8473,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A377" t="str">
         <f>B368</f>
         <v>perovskite cell curing 1</v>
@@ -8474,7 +8497,7 @@
         <v>cured perovskite cell 1</v>
       </c>
     </row>
-    <row r="378" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
         <v>258</v>
       </c>
@@ -8495,7 +8518,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
         <v>51</v>
       </c>
@@ -8516,7 +8539,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="380" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
         <v>206</v>
       </c>
@@ -8540,7 +8563,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
         <v>114</v>
       </c>
@@ -8564,7 +8587,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
         <v>95</v>
       </c>
@@ -8585,7 +8608,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
         <v>130</v>
       </c>
@@ -8606,7 +8629,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
         <v>206</v>
       </c>
@@ -8630,9 +8653,9 @@
         <v>207</v>
       </c>
     </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B385">
         <f>-87660/35066568.3948119</f>
@@ -8648,29 +8671,31 @@
         <v>77</v>
       </c>
       <c r="G385" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H385" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="388" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="387" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="388" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A388" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="389" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A389" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B389" s="5" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.2">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
         <v>3</v>
       </c>
@@ -8678,7 +8703,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
         <v>5</v>
       </c>
@@ -8686,15 +8711,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
         <v>6</v>
       </c>
       <c r="B392" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.2">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
         <v>7</v>
       </c>
@@ -8702,7 +8727,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
         <v>8</v>
       </c>
@@ -8710,7 +8735,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A395" s="1" t="s">
         <v>9</v>
       </c>
@@ -8721,7 +8746,7 @@
       <c r="F395" s="1"/>
       <c r="G395" s="1"/>
     </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A396" s="1" t="s">
         <v>10</v>
       </c>
@@ -8747,7 +8772,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A397" t="str">
         <f>B388</f>
         <v>perovskite cell zinc oxide deposition</v>
@@ -8771,9 +8796,9 @@
         <v>zinc oxide deposited perovskite cell</v>
       </c>
     </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B398">
         <f>35066568.3948119/35016480.9441634</f>
@@ -8789,12 +8814,12 @@
         <v>77</v>
       </c>
       <c r="G398" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.2">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="399" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B399">
         <f>70/35016480.9441634</f>
@@ -8810,10 +8835,10 @@
         <v>77</v>
       </c>
       <c r="G399" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.2">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="400" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
         <v>115</v>
       </c>
@@ -8834,10 +8859,10 @@
         <v>116</v>
       </c>
       <c r="H400" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.2">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
         <v>145</v>
       </c>
@@ -8858,10 +8883,10 @@
         <v>146</v>
       </c>
       <c r="H401" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.2">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="402" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
         <v>117</v>
       </c>
@@ -8882,10 +8907,10 @@
         <v>118</v>
       </c>
       <c r="H402" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="403" spans="1:8" x14ac:dyDescent="0.2">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="403" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
         <v>51</v>
       </c>
@@ -8906,7 +8931,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="404" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
         <v>206</v>
       </c>
@@ -8930,7 +8955,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
         <v>114</v>
       </c>
@@ -8954,7 +8979,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="406" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
         <v>95</v>
       </c>
@@ -8975,7 +9000,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="407" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
         <v>130</v>
       </c>
@@ -8996,9 +9021,9 @@
         <v>131</v>
       </c>
     </row>
-    <row r="408" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B408">
         <f>-438300/35016480.9441634</f>
@@ -9014,13 +9039,13 @@
         <v>77</v>
       </c>
       <c r="G408" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H408" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="409" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
         <v>206</v>
       </c>
@@ -9044,23 +9069,25 @@
         <v>207</v>
       </c>
     </row>
-    <row r="412" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="411" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="412" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A412" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="413" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="413" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A413" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B413" s="5" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="414" spans="1:8" x14ac:dyDescent="0.2">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="414" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
         <v>3</v>
       </c>
@@ -9068,7 +9095,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="415" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
         <v>5</v>
       </c>
@@ -9076,15 +9103,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="416" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
         <v>6</v>
       </c>
       <c r="B416" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="417" spans="1:8" x14ac:dyDescent="0.2">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="417" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
         <v>7</v>
       </c>
@@ -9092,7 +9119,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="418" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
         <v>8</v>
       </c>
@@ -9100,7 +9127,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="419" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A419" s="1" t="s">
         <v>9</v>
       </c>
@@ -9111,7 +9138,7 @@
       <c r="F419" s="1"/>
       <c r="G419" s="1"/>
     </row>
-    <row r="420" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A420" s="1" t="s">
         <v>10</v>
       </c>
@@ -9137,7 +9164,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="421" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A421" t="str">
         <f>B412</f>
         <v>sputter process 3, perovskite cell</v>
@@ -9161,9 +9188,9 @@
         <v>perovskite cell, sputtered 3</v>
       </c>
     </row>
-    <row r="422" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B422" s="3">
         <f>35016480.9441634/34966393.4935149</f>
@@ -9179,10 +9206,10 @@
         <v>77</v>
       </c>
       <c r="G422" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="423" spans="1:8" x14ac:dyDescent="0.2">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="423" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
         <v>217</v>
       </c>
@@ -9203,7 +9230,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="424" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
         <v>115</v>
       </c>
@@ -9224,10 +9251,10 @@
         <v>116</v>
       </c>
       <c r="H424" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="425" spans="1:8" x14ac:dyDescent="0.2">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="425" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
         <v>145</v>
       </c>
@@ -9248,10 +9275,10 @@
         <v>146</v>
       </c>
       <c r="H425" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="426" spans="1:8" x14ac:dyDescent="0.2">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="426" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
         <v>117</v>
       </c>
@@ -9272,10 +9299,10 @@
         <v>118</v>
       </c>
       <c r="H426" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="427" spans="1:8" x14ac:dyDescent="0.2">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="427" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
         <v>51</v>
       </c>
@@ -9296,7 +9323,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="428" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
         <v>206</v>
       </c>
@@ -9320,7 +9347,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="429" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
         <v>114</v>
       </c>
@@ -9344,7 +9371,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="430" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
         <v>95</v>
       </c>
@@ -9365,7 +9392,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="431" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
         <v>130</v>
       </c>
@@ -9386,7 +9413,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="432" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
         <v>206</v>
       </c>
@@ -9410,9 +9437,9 @@
         <v>207</v>
       </c>
     </row>
-    <row r="433" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B433">
         <f>-2629800/34966393.4935149</f>
@@ -9428,29 +9455,31 @@
         <v>77</v>
       </c>
       <c r="G433" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H433" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="436" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="435" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="436" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A436" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="437" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="437" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A437" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B437" s="5" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="438" spans="1:8" x14ac:dyDescent="0.2">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="438" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
         <v>3</v>
       </c>
@@ -9458,7 +9487,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="439" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
         <v>5</v>
       </c>
@@ -9466,15 +9495,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="440" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
         <v>6</v>
       </c>
       <c r="B440" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="441" spans="1:8" x14ac:dyDescent="0.2">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="441" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
         <v>7</v>
       </c>
@@ -9482,7 +9511,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="442" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
         <v>8</v>
       </c>
@@ -9490,7 +9519,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="443" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A443" s="1" t="s">
         <v>9</v>
       </c>
@@ -9501,7 +9530,7 @@
       <c r="F443" s="1"/>
       <c r="G443" s="1"/>
     </row>
-    <row r="444" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A444" s="1" t="s">
         <v>10</v>
       </c>
@@ -9527,7 +9556,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="445" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A445" t="str">
         <f>B436</f>
         <v>perovskite cell contact formation</v>
@@ -9551,9 +9580,9 @@
         <v>metallized perovskite cell</v>
       </c>
     </row>
-    <row r="446" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B446">
         <f>34966393.4935149/34916306.0428664</f>
@@ -9569,10 +9598,10 @@
         <v>77</v>
       </c>
       <c r="G446" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="447" spans="1:8" x14ac:dyDescent="0.2">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="447" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
         <v>250</v>
       </c>
@@ -9590,12 +9619,12 @@
         <v>77</v>
       </c>
       <c r="G447" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="448" spans="1:8" x14ac:dyDescent="0.2">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="448" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B448">
         <f>3800.95/34916306.0428664</f>
@@ -9611,10 +9640,10 @@
         <v>77</v>
       </c>
       <c r="G448" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="449" spans="1:8" x14ac:dyDescent="0.2">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="449" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
         <v>51</v>
       </c>
@@ -9635,7 +9664,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="450" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
         <v>147</v>
       </c>
@@ -9656,9 +9685,9 @@
         <v>56</v>
       </c>
     </row>
-    <row r="451" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B451">
         <f>0.0000008002/34916306.0428664</f>
@@ -9674,12 +9703,12 @@
         <v>77</v>
       </c>
       <c r="G451" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="452" spans="1:8" x14ac:dyDescent="0.2">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="452" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B452">
         <f>100.025/34916306.0428664</f>
@@ -9695,10 +9724,10 @@
         <v>77</v>
       </c>
       <c r="G452" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="453" spans="1:8" x14ac:dyDescent="0.2">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="453" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
         <v>94</v>
       </c>
@@ -9719,9 +9748,9 @@
         <v>156</v>
       </c>
     </row>
-    <row r="454" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B454">
         <f>87.6219/34916306.0428664</f>
@@ -9737,12 +9766,12 @@
         <v>77</v>
       </c>
       <c r="G454" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="455" spans="1:8" x14ac:dyDescent="0.2">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="455" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B455">
         <f>685.3713/34916306.0428664</f>
@@ -9761,9 +9790,9 @@
         <v>157</v>
       </c>
     </row>
-    <row r="456" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B456">
         <f>3500/50.7/34916306.0428664</f>
@@ -9779,12 +9808,12 @@
         <v>77</v>
       </c>
       <c r="G456" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="457" spans="1:8" x14ac:dyDescent="0.2">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="457" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B457">
         <f>24500/34916306.0428664</f>
@@ -9800,12 +9829,12 @@
         <v>77</v>
       </c>
       <c r="G457" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="458" spans="1:8" x14ac:dyDescent="0.2">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="458" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B458">
         <f>70000/34916306.0428664</f>
@@ -9821,10 +9850,10 @@
         <v>77</v>
       </c>
       <c r="G458" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="459" spans="1:8" x14ac:dyDescent="0.2">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="459" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
         <v>114</v>
       </c>
@@ -9848,7 +9877,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="460" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
         <v>95</v>
       </c>
@@ -9869,7 +9898,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="461" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
         <v>130</v>
       </c>
@@ -9890,9 +9919,9 @@
         <v>131</v>
       </c>
     </row>
-    <row r="462" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B462">
         <f>-200/34916306.0428664</f>
@@ -9908,12 +9937,12 @@
         <v>77</v>
       </c>
       <c r="G462" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="463" spans="1:8" x14ac:dyDescent="0.2">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="463" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B463">
         <f>-1391.66666666667/34916306.0428664</f>
@@ -9929,12 +9958,12 @@
         <v>77</v>
       </c>
       <c r="G463" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="464" spans="1:8" x14ac:dyDescent="0.2">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="464" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B464">
         <f>-28489500/34916306.0428664</f>
@@ -9950,29 +9979,31 @@
         <v>77</v>
       </c>
       <c r="G464" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H464" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="467" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="466" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="467" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A467" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="468" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="468" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A468" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B468" s="5" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="469" spans="1:8" x14ac:dyDescent="0.2">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="469" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
         <v>3</v>
       </c>
@@ -9980,7 +10011,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="470" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
         <v>5</v>
       </c>
@@ -9988,15 +10019,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="471" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
         <v>6</v>
       </c>
       <c r="B471" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="472" spans="1:8" x14ac:dyDescent="0.2">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="472" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
         <v>7</v>
       </c>
@@ -10004,7 +10035,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="473" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
         <v>8</v>
       </c>
@@ -10012,7 +10043,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="474" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A474" s="1" t="s">
         <v>9</v>
       </c>
@@ -10023,7 +10054,7 @@
       <c r="F474" s="1"/>
       <c r="G474" s="1"/>
     </row>
-    <row r="475" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A475" s="1" t="s">
         <v>10</v>
       </c>
@@ -10049,7 +10080,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="476" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A476" t="str">
         <f>B467</f>
         <v>perovskite cell curing 2</v>
@@ -10073,9 +10104,9 @@
         <v>cured perovskite cell 2</v>
       </c>
     </row>
-    <row r="477" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B477">
         <f>34916306.0428664/34866218.5922179</f>
@@ -10091,10 +10122,10 @@
         <v>77</v>
       </c>
       <c r="G477" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="478" spans="1:8" x14ac:dyDescent="0.2">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="478" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
         <v>51</v>
       </c>
@@ -10115,7 +10146,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="479" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
         <v>114</v>
       </c>
@@ -10139,7 +10170,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="480" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
         <v>95</v>
       </c>
@@ -10160,7 +10191,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="481" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
         <v>130</v>
       </c>
@@ -10181,9 +10212,9 @@
         <v>131</v>
       </c>
     </row>
-    <row r="482" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B482">
         <f>-(43830000+5697900)/34866218.5922179</f>
@@ -10199,13 +10230,13 @@
         <v>77</v>
       </c>
       <c r="G482" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H482" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="483" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
         <v>144</v>
       </c>
@@ -10226,26 +10257,28 @@
         <v>143</v>
       </c>
       <c r="H483" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="486" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="484" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="485" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="486" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A486" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="487" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="487" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A487" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B487" s="5" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="488" spans="1:8" x14ac:dyDescent="0.2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="488" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
         <v>3</v>
       </c>
@@ -10253,7 +10286,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="489" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
         <v>5</v>
       </c>
@@ -10261,15 +10294,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="490" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
         <v>6</v>
       </c>
       <c r="B490" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="491" spans="1:8" x14ac:dyDescent="0.2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="491" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
         <v>7</v>
       </c>
@@ -10277,7 +10310,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="492" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
         <v>8</v>
       </c>
@@ -10285,7 +10318,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="493" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A493" s="1" t="s">
         <v>9</v>
       </c>
@@ -10296,7 +10329,7 @@
       <c r="F493" s="1"/>
       <c r="G493" s="1"/>
     </row>
-    <row r="494" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A494" s="1" t="s">
         <v>10</v>
       </c>
@@ -10322,7 +10355,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="495" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A495" t="str">
         <f>B486</f>
         <v>photovoltaic cell production, perovskite</v>
@@ -10346,9 +10379,9 @@
         <v>photovoltaic cell, perovskite</v>
       </c>
     </row>
-    <row r="496" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B496">
         <f>34866218.5922179/34816131.1415694</f>
@@ -10364,10 +10397,10 @@
         <v>77</v>
       </c>
       <c r="G496" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="497" spans="1:8" x14ac:dyDescent="0.2">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="497" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
         <v>51</v>
       </c>
@@ -10388,7 +10421,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="498" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
         <v>114</v>
       </c>
@@ -10412,7 +10445,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="499" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
         <v>95</v>
       </c>
@@ -10433,7 +10466,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="500" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
         <v>130</v>
       </c>
@@ -10454,23 +10487,24 @@
         <v>131</v>
       </c>
     </row>
-    <row r="502" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="502" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A502" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="503" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="503" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A503" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B503" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="504" spans="1:8" x14ac:dyDescent="0.2">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="504" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
         <v>3</v>
       </c>
@@ -10478,7 +10512,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="505" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
         <v>5</v>
       </c>
@@ -10486,15 +10520,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="506" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
         <v>6</v>
       </c>
       <c r="B506" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="507" spans="1:8" x14ac:dyDescent="0.2">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="507" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
         <v>7</v>
       </c>
@@ -10502,7 +10536,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="508" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
         <v>8</v>
       </c>
@@ -10510,7 +10544,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="509" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A509" s="1" t="s">
         <v>9</v>
       </c>
@@ -10521,7 +10555,7 @@
       <c r="F509" s="1"/>
       <c r="G509" s="1"/>
     </row>
-    <row r="510" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A510" s="1" t="s">
         <v>10</v>
       </c>
@@ -10547,7 +10581,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="511" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A511" t="str">
         <f>B502</f>
         <v>perovskite photovoltaic module assembly</v>
@@ -10567,12 +10601,12 @@
         <v>14</v>
       </c>
       <c r="G511" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="512" spans="1:8" x14ac:dyDescent="0.2">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="512" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B512" s="3">
         <v>36.001438685192085</v>
@@ -10587,12 +10621,12 @@
         <v>77</v>
       </c>
       <c r="G512" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="513" spans="1:8" x14ac:dyDescent="0.2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="513" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B513">
         <v>3.3530571992109896E-2</v>
@@ -10607,15 +10641,15 @@
         <v>77</v>
       </c>
       <c r="G513" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H513" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="514" spans="1:8" x14ac:dyDescent="0.2">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="514" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B514">
         <v>7.7655547329470845E-2</v>
@@ -10630,15 +10664,15 @@
         <v>77</v>
       </c>
       <c r="G514" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H514" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="515" spans="1:8" x14ac:dyDescent="0.2">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="515" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B515">
         <v>7.7655547329470845E-2</v>
@@ -10653,15 +10687,15 @@
         <v>77</v>
       </c>
       <c r="G515" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H515" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="516" spans="1:8" x14ac:dyDescent="0.2">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="516" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B516">
         <v>4.9975384243020806E-3</v>
@@ -10676,15 +10710,15 @@
         <v>77</v>
       </c>
       <c r="G516" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H516" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="517" spans="1:8" x14ac:dyDescent="0.2">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="517" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B517">
         <v>4.9975384243020806E-3</v>
@@ -10699,15 +10733,15 @@
         <v>77</v>
       </c>
       <c r="G517" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H517" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="518" spans="1:8" x14ac:dyDescent="0.2">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="518" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A518" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B518">
         <v>11.374492585831344</v>
@@ -10722,12 +10756,12 @@
         <v>77</v>
       </c>
       <c r="G518" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="519" spans="1:8" x14ac:dyDescent="0.2">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="519" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B519">
         <v>3.9086892704038624E-2</v>
@@ -10742,13 +10776,13 @@
         <v>77</v>
       </c>
       <c r="G519" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H519" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="520" spans="1:8" x14ac:dyDescent="0.2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="520" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
         <v>51</v>
       </c>
@@ -10768,10 +10802,10 @@
         <v>52</v>
       </c>
       <c r="H520" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="521" spans="1:8" x14ac:dyDescent="0.2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="521" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
         <v>55</v>
       </c>
@@ -10791,12 +10825,12 @@
         <v>56</v>
       </c>
       <c r="H521" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="522" spans="1:8" x14ac:dyDescent="0.2">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="522" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B522">
         <v>3.4743904625812109E-4</v>
@@ -10811,15 +10845,15 @@
         <v>77</v>
       </c>
       <c r="G522" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H522" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="523" spans="1:8" x14ac:dyDescent="0.2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="523" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B523">
         <v>0.25851119513253057</v>
@@ -10834,12 +10868,12 @@
         <v>77</v>
       </c>
       <c r="G523" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="524" spans="1:8" x14ac:dyDescent="0.2">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="524" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B524">
         <v>0.1835429485440967</v>
@@ -10854,12 +10888,12 @@
         <v>77</v>
       </c>
       <c r="G524" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="525" spans="1:8" x14ac:dyDescent="0.2">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="525" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B525">
         <v>2.8436231464578365E-2</v>
@@ -10874,12 +10908,12 @@
         <v>77</v>
       </c>
       <c r="G525" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="526" spans="1:8" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="526" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B526">
         <v>4.6532015123855505E-2</v>
@@ -10894,12 +10928,12 @@
         <v>77</v>
       </c>
       <c r="G526" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="527" spans="1:8" x14ac:dyDescent="0.2">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="527" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B527">
         <v>1.5510671707951835E-3</v>
@@ -10914,10 +10948,10 @@
         <v>77</v>
       </c>
       <c r="G527" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="528" spans="1:8" x14ac:dyDescent="0.2">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="528" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
         <v>84</v>
       </c>
@@ -10937,9 +10971,9 @@
         <v>124</v>
       </c>
     </row>
-    <row r="529" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B529">
         <v>7.7656763017812186E-2</v>
@@ -10954,13 +10988,13 @@
         <v>77</v>
       </c>
       <c r="G529" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H529" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="530" spans="1:8" x14ac:dyDescent="0.2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="530" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
         <v>51</v>
       </c>
@@ -10980,10 +11014,10 @@
         <v>52</v>
       </c>
       <c r="H530" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="531" spans="1:8" x14ac:dyDescent="0.2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="531" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
         <v>55</v>
       </c>
@@ -11003,10 +11037,10 @@
         <v>56</v>
       </c>
       <c r="H531" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="532" spans="1:8" x14ac:dyDescent="0.2">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="532" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
         <v>51</v>
       </c>
@@ -11026,10 +11060,10 @@
         <v>52</v>
       </c>
       <c r="H532" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="533" spans="1:8" x14ac:dyDescent="0.2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="533" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
         <v>206</v>
       </c>
@@ -11052,7 +11086,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="534" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
         <v>114</v>
       </c>
@@ -11075,9 +11109,9 @@
         <v>209</v>
       </c>
     </row>
-    <row r="535" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B535">
         <v>5.1702239026506112E-3</v>
@@ -11092,12 +11126,12 @@
         <v>77</v>
       </c>
       <c r="G535" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="536" spans="1:8" x14ac:dyDescent="0.2">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="536" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B536">
         <v>-5.1702239026506112E-3</v>
@@ -11112,10 +11146,10 @@
         <v>77</v>
       </c>
       <c r="G536" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="537" spans="1:8" x14ac:dyDescent="0.2">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="537" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
         <v>95</v>
       </c>
@@ -11135,7 +11169,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="538" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
         <v>130</v>
       </c>
@@ -11155,7 +11189,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="539" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
         <v>206</v>
       </c>
@@ -11178,23 +11212,25 @@
         <v>207</v>
       </c>
     </row>
-    <row r="542" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="541" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="542" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A542" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="543" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="543" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A543" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B543" s="5" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="544" spans="1:8" x14ac:dyDescent="0.2">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="544" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
         <v>3</v>
       </c>
@@ -11202,7 +11238,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="545" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
         <v>5</v>
       </c>
@@ -11210,15 +11246,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="546" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
         <v>6</v>
       </c>
       <c r="B546" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="547" spans="1:8" x14ac:dyDescent="0.2">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="547" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
         <v>7</v>
       </c>
@@ -11226,7 +11262,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="548" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
         <v>8</v>
       </c>
@@ -11234,7 +11270,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="549" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A549" s="1" t="s">
         <v>9</v>
       </c>
@@ -11245,7 +11281,7 @@
       <c r="F549" s="1"/>
       <c r="G549" s="1"/>
     </row>
-    <row r="550" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A550" s="1" t="s">
         <v>10</v>
       </c>
@@ -11271,7 +11307,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="551" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A551" t="str">
         <f>B542</f>
         <v>photovoltaic panel installation, 0.5kWp, perovskite</v>
@@ -11295,9 +11331,9 @@
         <v>photovoltaic panel, perovskite</v>
       </c>
     </row>
-    <row r="552" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B552" s="3">
         <v>2</v>
@@ -11312,15 +11348,15 @@
         <v>77</v>
       </c>
       <c r="G552" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H552" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="553" spans="1:8" x14ac:dyDescent="0.2">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="553" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B553">
         <f>24176.902655205/483538.053104108</f>
@@ -11336,12 +11372,12 @@
         <v>77</v>
       </c>
       <c r="G553" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="554" spans="1:8" x14ac:dyDescent="0.2">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="554" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B554">
         <f>589916.424787002/483538.053104108</f>
@@ -11357,26 +11393,27 @@
         <v>77</v>
       </c>
       <c r="G554" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="556" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="555" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="556" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A556" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B556" s="2" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="557" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="557" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A557" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B557" s="8" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="558" spans="1:8" x14ac:dyDescent="0.2">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="558" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
         <v>3</v>
       </c>
@@ -11384,7 +11421,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="559" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
         <v>5</v>
       </c>
@@ -11392,15 +11429,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="560" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
         <v>6</v>
       </c>
       <c r="B560" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="561" spans="1:12" x14ac:dyDescent="0.2">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="561" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
         <v>7</v>
       </c>
@@ -11408,7 +11445,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="562" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
         <v>8</v>
       </c>
@@ -11416,7 +11453,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="563" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A563" s="1" t="s">
         <v>9</v>
       </c>
@@ -11427,7 +11464,7 @@
       <c r="F563" s="1"/>
       <c r="G563" s="1"/>
     </row>
-    <row r="564" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A564" s="1" t="s">
         <v>10</v>
       </c>
@@ -11453,19 +11490,19 @@
         <v>2</v>
       </c>
       <c r="I564" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J564" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K564" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L564" s="1" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="565" spans="1:12" x14ac:dyDescent="0.2">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="565" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A565" t="str">
         <f>B556</f>
         <v>electricity production, photovoltaic, 0.5kWp, perovskite-on-silicon tandem</v>
@@ -11490,9 +11527,9 @@
         <v>electricity production, photovoltaic, 0.5kWp, perovskite-on-silicon tandem</v>
       </c>
     </row>
-    <row r="566" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B566" s="4">
         <f>1/(25*460)</f>
@@ -11508,7 +11545,7 @@
         <v>77</v>
       </c>
       <c r="G566" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="I566" s="7">
         <v>5</v>
@@ -11526,23 +11563,24 @@
         <v>1.0869565217391305E-4</v>
       </c>
     </row>
-    <row r="568" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:12" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="568" spans="1:12" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A568" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="569" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="569" spans="1:12" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A569" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B569" s="5" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="570" spans="1:12" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="570" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
         <v>3</v>
       </c>
@@ -11550,7 +11588,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="571" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
         <v>5</v>
       </c>
@@ -11558,15 +11596,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="572" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
         <v>6</v>
       </c>
       <c r="B572" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="573" spans="1:12" x14ac:dyDescent="0.2">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="573" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A573" t="s">
         <v>7</v>
       </c>
@@ -11574,7 +11612,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="574" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A574" t="s">
         <v>8</v>
       </c>
@@ -11582,7 +11620,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="575" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A575" s="1" t="s">
         <v>9</v>
       </c>
@@ -11593,7 +11631,7 @@
       <c r="F575" s="1"/>
       <c r="G575" s="1"/>
     </row>
-    <row r="576" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A576" s="1" t="s">
         <v>10</v>
       </c>
@@ -11619,7 +11657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="577" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A577" t="str">
         <f>B568</f>
         <v>exhaust abatement, for perovskite</v>
@@ -11644,10 +11682,10 @@
         <v>abated exhaust</v>
       </c>
       <c r="H577" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="578" spans="1:8" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="578" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A578" t="s">
         <v>106</v>
       </c>
@@ -11667,7 +11705,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="579" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A579" t="s">
         <v>100</v>
       </c>
@@ -11687,7 +11725,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="580" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A580" t="s">
         <v>51</v>
       </c>
@@ -11708,10 +11746,10 @@
         <v>52</v>
       </c>
       <c r="H580" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="581" spans="1:8" x14ac:dyDescent="0.2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="581" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A581" t="s">
         <v>113</v>
       </c>
@@ -11734,9 +11772,9 @@
         <v>210</v>
       </c>
     </row>
-    <row r="582" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A582" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B582">
         <v>0.23200000000000001</v>
@@ -11751,13 +11789,13 @@
         <v>77</v>
       </c>
       <c r="G582" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H582" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="583" spans="1:8" x14ac:dyDescent="0.2">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="583" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A583" t="s">
         <v>114</v>
       </c>
@@ -11780,9 +11818,9 @@
         <v>209</v>
       </c>
     </row>
-    <row r="584" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A584" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B584">
         <v>0</v>
@@ -11797,12 +11835,12 @@
         <v>78</v>
       </c>
       <c r="H584" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="585" spans="1:8" x14ac:dyDescent="0.2">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="585" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A585" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B585">
         <v>0</v>
@@ -11817,12 +11855,12 @@
         <v>78</v>
       </c>
       <c r="H585" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="586" spans="1:8" x14ac:dyDescent="0.2">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="586" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A586" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B586">
         <v>0</v>
@@ -11837,12 +11875,12 @@
         <v>78</v>
       </c>
       <c r="H586" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="587" spans="1:8" x14ac:dyDescent="0.2">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="587" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A587" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B587">
         <v>0</v>
@@ -11857,10 +11895,12 @@
         <v>78</v>
       </c>
       <c r="H587" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="590" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="588" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="589" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="590" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A590" s="2" t="s">
         <v>1</v>
       </c>
@@ -11868,15 +11908,15 @@
         <v>144</v>
       </c>
     </row>
-    <row r="591" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A591" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B591" s="5" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="592" spans="1:8" x14ac:dyDescent="0.2">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="592" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A592" t="s">
         <v>3</v>
       </c>
@@ -11884,7 +11924,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="593" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A593" t="s">
         <v>5</v>
       </c>
@@ -11892,7 +11932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="594" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A594" t="s">
         <v>6</v>
       </c>
@@ -11900,7 +11940,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="595" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A595" t="s">
         <v>7</v>
       </c>
@@ -11908,7 +11948,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="596" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A596" t="s">
         <v>8</v>
       </c>
@@ -11916,7 +11956,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="597" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A597" s="1" t="s">
         <v>9</v>
       </c>
@@ -11927,7 +11967,7 @@
       <c r="F597" s="1"/>
       <c r="G597" s="1"/>
     </row>
-    <row r="598" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A598" s="1" t="s">
         <v>10</v>
       </c>
@@ -11953,7 +11993,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="599" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A599" t="str">
         <f>B590</f>
         <v>tray cleaning, for perovskite</v>
@@ -11976,12 +12016,12 @@
         <v>tray cleaning</v>
       </c>
       <c r="H599" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="600" spans="1:8" x14ac:dyDescent="0.2">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="600" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A600" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B600">
         <f>2.10977682373547E-07/0.7</f>
@@ -11997,13 +12037,13 @@
         <v>77</v>
       </c>
       <c r="G600" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H600" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="601" spans="1:8" x14ac:dyDescent="0.2">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="601" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A601" t="s">
         <v>100</v>
       </c>
@@ -12024,7 +12064,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="602" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A602" t="s">
         <v>51</v>
       </c>
@@ -12045,12 +12085,12 @@
         <v>52</v>
       </c>
       <c r="H602" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="603" spans="1:8" x14ac:dyDescent="0.2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="603" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A603" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B603">
         <f>3.97134460938441E-06*1000</f>
@@ -12072,7 +12112,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="604" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A604" t="s">
         <v>93</v>
       </c>
@@ -12093,9 +12133,9 @@
         <v>157</v>
       </c>
     </row>
-    <row r="605" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A605" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B605">
         <f>-2.48209038086526E-06</f>
@@ -12111,12 +12151,12 @@
         <v>77</v>
       </c>
       <c r="G605" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="606" spans="1:8" x14ac:dyDescent="0.2">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="606" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A606" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B606">
         <f>-0.148925422851915</f>
@@ -12132,13 +12172,15 @@
         <v>77</v>
       </c>
       <c r="G606" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H606" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="609" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="608" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="609" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A609" s="2" t="s">
         <v>1</v>
       </c>
@@ -12146,7 +12188,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="610" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A610" s="5" t="s">
         <v>2</v>
       </c>
@@ -12154,7 +12196,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="611" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A611" t="s">
         <v>3</v>
       </c>
@@ -12162,7 +12204,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="612" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A612" t="s">
         <v>5</v>
       </c>
@@ -12170,7 +12212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="613" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A613" t="s">
         <v>6</v>
       </c>
@@ -12178,7 +12220,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="614" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A614" t="s">
         <v>7</v>
       </c>
@@ -12186,7 +12228,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="615" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A615" t="s">
         <v>8</v>
       </c>
@@ -12194,7 +12236,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="616" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A616" s="1" t="s">
         <v>9</v>
       </c>
@@ -12205,7 +12247,7 @@
       <c r="F616" s="1"/>
       <c r="G616" s="1"/>
     </row>
-    <row r="617" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A617" s="1" t="s">
         <v>10</v>
       </c>
@@ -12231,7 +12273,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="618" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A618" t="str">
         <f>B609</f>
         <v>ultrapure water system activity, for perovskite</v>
@@ -12257,7 +12299,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="619" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A619" t="s">
         <v>51</v>
       </c>
@@ -12278,12 +12320,12 @@
         <v>52</v>
       </c>
       <c r="H619" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="620" spans="1:8" x14ac:dyDescent="0.2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="620" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A620" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B620">
         <f>3.63854545454545*1000/2307.27272727273</f>
@@ -12305,7 +12347,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="621" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A621" t="s">
         <v>114</v>
       </c>
@@ -12329,9 +12371,9 @@
         <v>209</v>
       </c>
     </row>
-    <row r="622" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A622" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B622">
         <f>3.27272727272727E-07/2307.27272727273</f>
@@ -12347,10 +12389,10 @@
         <v>77</v>
       </c>
       <c r="G622" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="623" spans="1:8" x14ac:dyDescent="0.2">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="623" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A623" t="s">
         <v>252</v>
       </c>
@@ -12371,10 +12413,12 @@
         <v>253</v>
       </c>
       <c r="H623" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="626" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="624" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="625" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="626" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A626" s="2" t="s">
         <v>1</v>
       </c>
@@ -12382,7 +12426,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="627" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A627" s="5" t="s">
         <v>2</v>
       </c>
@@ -12390,7 +12434,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="628" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A628" t="s">
         <v>3</v>
       </c>
@@ -12398,7 +12442,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="629" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A629" t="s">
         <v>5</v>
       </c>
@@ -12406,7 +12450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="630" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A630" t="s">
         <v>6</v>
       </c>
@@ -12414,7 +12458,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="631" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A631" t="s">
         <v>7</v>
       </c>
@@ -12422,7 +12466,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="632" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A632" t="s">
         <v>8</v>
       </c>
@@ -12430,7 +12474,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="633" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A633" s="1" t="s">
         <v>9</v>
       </c>
@@ -12441,7 +12485,7 @@
       <c r="F633" s="1"/>
       <c r="G633" s="1"/>
     </row>
-    <row r="634" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A634" s="1" t="s">
         <v>10</v>
       </c>
@@ -12467,7 +12511,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="635" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A635" t="str">
         <f>B626</f>
         <v>inhouse waste water treatment, for perovskite production</v>
@@ -12494,7 +12538,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="636" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A636" t="s">
         <v>104</v>
       </c>
@@ -12515,10 +12559,10 @@
         <v>105</v>
       </c>
       <c r="H636" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="637" spans="1:8" x14ac:dyDescent="0.2">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="637" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A637" t="s">
         <v>100</v>
       </c>
@@ -12538,7 +12582,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="638" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A638" t="s">
         <v>25</v>
       </c>
@@ -12559,12 +12603,12 @@
         <v>111</v>
       </c>
       <c r="H638" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="639" spans="1:8" x14ac:dyDescent="0.2">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="639" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A639" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B639">
         <v>0.45705279747832939</v>
@@ -12579,12 +12623,12 @@
         <v>77</v>
       </c>
       <c r="G639" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="640" spans="1:8" x14ac:dyDescent="0.2">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="640" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A640" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B640">
         <v>0.33884948778565799</v>
@@ -12599,12 +12643,12 @@
         <v>77</v>
       </c>
       <c r="G640" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="641" spans="1:8" x14ac:dyDescent="0.2">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="641" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A641" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B641">
         <v>0.42111899133175729</v>
@@ -12619,10 +12663,10 @@
         <v>77</v>
       </c>
       <c r="G641" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="642" spans="1:8" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="642" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A642" t="s">
         <v>51</v>
       </c>
@@ -12643,10 +12687,10 @@
         <v>52</v>
       </c>
       <c r="H642" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="643" spans="1:8" x14ac:dyDescent="0.2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="643" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A643" t="s">
         <v>114</v>
       </c>
@@ -12670,9 +12714,9 @@
         <v>209</v>
       </c>
     </row>
-    <row r="644" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A644" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B644">
         <v>315.20882584712399</v>
@@ -12693,7 +12737,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="645" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A645" t="s">
         <v>252</v>
       </c>
@@ -12713,12 +12757,12 @@
         <v>253</v>
       </c>
       <c r="H645" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="646" spans="1:8" x14ac:dyDescent="0.2">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="646" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A646" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B646">
         <f>-0.179790569157611*1000</f>
@@ -12734,12 +12778,12 @@
         <v>77</v>
       </c>
       <c r="G646" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="647" spans="1:8" x14ac:dyDescent="0.2">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="647" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A647" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B647">
         <f>-78.8022064617809</f>
@@ -12755,15 +12799,15 @@
         <v>77</v>
       </c>
       <c r="G647" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H647" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="648" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A648" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B648">
         <v>-47.281323877068601</v>
@@ -12778,13 +12822,15 @@
         <v>77</v>
       </c>
       <c r="G648" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H648" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="651" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="650" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="651" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A651" s="2" t="s">
         <v>1</v>
       </c>
@@ -12792,7 +12838,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="652" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A652" s="5" t="s">
         <v>2</v>
       </c>
@@ -12800,7 +12846,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="653" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A653" t="s">
         <v>3</v>
       </c>
@@ -12808,7 +12854,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="654" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A654" t="s">
         <v>5</v>
       </c>
@@ -12816,7 +12862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="655" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A655" t="s">
         <v>6</v>
       </c>
@@ -12824,7 +12870,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="656" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A656" t="s">
         <v>7</v>
       </c>
@@ -12832,7 +12878,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="657" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A657" t="s">
         <v>8</v>
       </c>
@@ -12840,7 +12886,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="658" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A658" s="1" t="s">
         <v>9</v>
       </c>
@@ -12851,7 +12897,7 @@
       <c r="F658" s="1"/>
       <c r="G658" s="1"/>
     </row>
-    <row r="659" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A659" s="1" t="s">
         <v>10</v>
       </c>
@@ -12877,7 +12923,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="660" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A660" t="str">
         <f>B651</f>
         <v>process cooling, water, for perovskite</v>
@@ -12903,7 +12949,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="661" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A661" t="s">
         <v>252</v>
       </c>
@@ -12923,10 +12969,10 @@
         <v>253</v>
       </c>
       <c r="H661" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="662" spans="1:8" x14ac:dyDescent="0.2">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="662" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A662" t="s">
         <v>51</v>
       </c>
@@ -12947,9 +12993,9 @@
         <v>52</v>
       </c>
     </row>
-    <row r="663" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A663" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B663">
         <v>1000</v>
@@ -12970,7 +13016,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="665" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="665" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A665" s="2" t="s">
         <v>1</v>
       </c>
@@ -12978,7 +13025,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="666" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A666" s="5" t="s">
         <v>2</v>
       </c>
@@ -12986,7 +13033,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="667" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A667" t="s">
         <v>3</v>
       </c>
@@ -12994,7 +13041,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="668" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A668" t="s">
         <v>5</v>
       </c>
@@ -13002,7 +13049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="669" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A669" t="s">
         <v>6</v>
       </c>
@@ -13010,7 +13057,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="670" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A670" t="s">
         <v>7</v>
       </c>
@@ -13018,7 +13065,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="671" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A671" t="s">
         <v>8</v>
       </c>
@@ -13026,7 +13073,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="672" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A672" s="1" t="s">
         <v>9</v>
       </c>
@@ -13037,7 +13084,7 @@
       <c r="F672" s="1"/>
       <c r="G672" s="1"/>
     </row>
-    <row r="673" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A673" s="1" t="s">
         <v>10</v>
       </c>
@@ -13063,7 +13110,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="674" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A674" t="str">
         <f>B665</f>
         <v>process cooling, water, for perovskite</v>
@@ -13090,7 +13137,9 @@
         <v>207</v>
       </c>
     </row>
-    <row r="677" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="676" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="677" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A677" s="2" t="s">
         <v>1</v>
       </c>
@@ -13098,7 +13147,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="678" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A678" s="5" t="s">
         <v>2</v>
       </c>
@@ -13106,7 +13155,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="679" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A679" t="s">
         <v>3</v>
       </c>
@@ -13114,7 +13163,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="680" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A680" t="s">
         <v>5</v>
       </c>
@@ -13122,7 +13171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="681" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A681" t="s">
         <v>6</v>
       </c>
@@ -13130,7 +13179,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="682" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A682" t="s">
         <v>7</v>
       </c>
@@ -13138,7 +13187,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="683" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A683" t="s">
         <v>8</v>
       </c>
@@ -13146,7 +13195,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="684" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A684" s="1" t="s">
         <v>9</v>
       </c>
@@ -13157,7 +13206,7 @@
       <c r="F684" s="1"/>
       <c r="G684" s="1"/>
     </row>
-    <row r="685" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A685" s="1" t="s">
         <v>10</v>
       </c>
@@ -13183,7 +13232,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="686" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A686" t="str">
         <f>B677</f>
         <v>air compressor activity, for perovskite</v>
@@ -13209,9 +13258,9 @@
         <v>209</v>
       </c>
     </row>
-    <row r="687" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A687" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B687">
         <v>1</v>
@@ -13226,21 +13275,23 @@
         <v>77</v>
       </c>
       <c r="G687" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H687" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="690" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="688" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="689" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="690" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A690" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B690" s="1" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="691" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="691" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A691" s="5" t="s">
         <v>2</v>
       </c>
@@ -13248,7 +13299,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="692" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A692" t="s">
         <v>3</v>
       </c>
@@ -13256,7 +13307,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="693" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A693" t="s">
         <v>5</v>
       </c>
@@ -13264,15 +13315,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="694" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A694" t="s">
         <v>6</v>
       </c>
       <c r="B694" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="695" spans="1:8" x14ac:dyDescent="0.2">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="695" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A695" t="s">
         <v>7</v>
       </c>
@@ -13280,7 +13331,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="696" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A696" t="s">
         <v>8</v>
       </c>
@@ -13288,7 +13339,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="697" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A697" s="1" t="s">
         <v>9</v>
       </c>
@@ -13299,7 +13350,7 @@
       <c r="F697" s="1"/>
       <c r="G697" s="1"/>
     </row>
-    <row r="698" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A698" s="1" t="s">
         <v>10</v>
       </c>
@@ -13325,7 +13376,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="699" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A699" t="str">
         <f>B690</f>
         <v>process exhaust ventilators, general, for perovskite production</v>
@@ -13351,9 +13402,9 @@
         <v>211</v>
       </c>
     </row>
-    <row r="700" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A700" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B700">
         <v>7.6051410753669521E-7</v>
@@ -13368,12 +13419,12 @@
         <v>77</v>
       </c>
       <c r="G700" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="701" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A701" t="s">
         <v>392</v>
-      </c>
-    </row>
-    <row r="701" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A701" t="s">
-        <v>391</v>
       </c>
       <c r="B701">
         <v>7.6051410753669521E-7</v>
@@ -13388,10 +13439,10 @@
         <v>77</v>
       </c>
       <c r="G701" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="702" spans="1:8" x14ac:dyDescent="0.2">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="702" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A702" t="s">
         <v>51</v>
       </c>
@@ -13412,9 +13463,9 @@
         <v>52</v>
       </c>
     </row>
-    <row r="703" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A703" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B703">
         <v>1.1407711613050422E-5</v>
@@ -13429,10 +13480,10 @@
         <v>78</v>
       </c>
       <c r="H703" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="704" spans="1:8" x14ac:dyDescent="0.2">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="704" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A704" t="s">
         <v>190</v>
       </c>
@@ -13449,10 +13500,10 @@
         <v>78</v>
       </c>
       <c r="H704" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="705" spans="1:8" x14ac:dyDescent="0.2">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="705" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A705" t="s">
         <v>76</v>
       </c>
@@ -13469,18 +13520,20 @@
         <v>78</v>
       </c>
       <c r="H705" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="708" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="706" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="707" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="708" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A708" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B708" s="1" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="709" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="709" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A709" s="5" t="s">
         <v>2</v>
       </c>
@@ -13488,7 +13541,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="710" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A710" t="s">
         <v>3</v>
       </c>
@@ -13496,7 +13549,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="711" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A711" t="s">
         <v>5</v>
       </c>
@@ -13504,15 +13557,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="712" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A712" t="s">
         <v>6</v>
       </c>
       <c r="B712" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="713" spans="1:8" x14ac:dyDescent="0.2">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="713" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A713" t="s">
         <v>7</v>
       </c>
@@ -13520,7 +13573,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="714" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A714" t="s">
         <v>8</v>
       </c>
@@ -13528,7 +13581,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="715" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A715" s="1" t="s">
         <v>9</v>
       </c>
@@ -13539,7 +13592,7 @@
       <c r="F715" s="1"/>
       <c r="G715" s="1"/>
     </row>
-    <row r="716" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A716" s="1" t="s">
         <v>10</v>
       </c>
@@ -13565,7 +13618,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="717" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A717" t="str">
         <f>B708</f>
         <v>process exhaust ventilators, acidic, for perovskite production</v>
@@ -13591,9 +13644,9 @@
         <v>211</v>
       </c>
     </row>
-    <row r="718" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A718" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B718">
         <v>7.6051410753669521E-7</v>
@@ -13608,12 +13661,12 @@
         <v>77</v>
       </c>
       <c r="G718" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="719" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A719" t="s">
         <v>392</v>
-      </c>
-    </row>
-    <row r="719" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A719" t="s">
-        <v>391</v>
       </c>
       <c r="B719">
         <v>7.6051410753669521E-7</v>
@@ -13628,10 +13681,10 @@
         <v>77</v>
       </c>
       <c r="G719" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="720" spans="1:8" x14ac:dyDescent="0.2">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="720" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A720" t="s">
         <v>51</v>
       </c>
@@ -13652,9 +13705,9 @@
         <v>52</v>
       </c>
     </row>
-    <row r="721" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A721" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B721">
         <v>1.1407711613050422E-5</v>
@@ -13669,10 +13722,10 @@
         <v>78</v>
       </c>
       <c r="H721" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="722" spans="1:8" x14ac:dyDescent="0.2">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="722" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A722" t="s">
         <v>190</v>
       </c>
@@ -13689,10 +13742,10 @@
         <v>78</v>
       </c>
       <c r="H722" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="723" spans="1:8" x14ac:dyDescent="0.2">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="723" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A723" t="s">
         <v>76</v>
       </c>
@@ -13709,10 +13762,10 @@
         <v>78</v>
       </c>
       <c r="H723" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="724" spans="1:8" x14ac:dyDescent="0.2">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="724" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A724" t="s">
         <v>25</v>
       </c>
@@ -13733,10 +13786,10 @@
         <v>111</v>
       </c>
       <c r="H724" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="725" spans="1:8" x14ac:dyDescent="0.2">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="725" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A725" t="s">
         <v>51</v>
       </c>
@@ -13757,7 +13810,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="726" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A726" t="s">
         <v>100</v>
       </c>
@@ -13777,15 +13830,17 @@
         <v>101</v>
       </c>
     </row>
-    <row r="729" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="728" spans="1:8" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="729" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A729" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B729" s="1" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="730" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="730" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A730" s="5" t="s">
         <v>2</v>
       </c>
@@ -13793,7 +13848,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="731" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A731" t="s">
         <v>3</v>
       </c>
@@ -13801,7 +13856,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="732" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A732" t="s">
         <v>5</v>
       </c>
@@ -13809,15 +13864,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="733" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A733" t="s">
         <v>6</v>
       </c>
       <c r="B733" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="734" spans="1:8" x14ac:dyDescent="0.2">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="734" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A734" t="s">
         <v>7</v>
       </c>
@@ -13825,7 +13880,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="735" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A735" t="s">
         <v>8</v>
       </c>
@@ -13833,7 +13888,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="736" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A736" s="1" t="s">
         <v>9</v>
       </c>
@@ -13844,7 +13899,7 @@
       <c r="F736" s="1"/>
       <c r="G736" s="1"/>
     </row>
-    <row r="737" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A737" s="1" t="s">
         <v>10</v>
       </c>
@@ -13870,7 +13925,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="738" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A738" t="str">
         <f>B729</f>
         <v>process exhaust ventilators, caustic, for perovskite production</v>
@@ -13896,9 +13951,9 @@
         <v>211</v>
       </c>
     </row>
-    <row r="739" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A739" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B739">
         <v>7.6051410753669521E-7</v>
@@ -13913,12 +13968,12 @@
         <v>77</v>
       </c>
       <c r="G739" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="740" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A740" t="s">
         <v>392</v>
-      </c>
-    </row>
-    <row r="740" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A740" t="s">
-        <v>391</v>
       </c>
       <c r="B740">
         <v>7.6051410753669521E-7</v>
@@ -13933,10 +13988,10 @@
         <v>77</v>
       </c>
       <c r="G740" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="741" spans="1:8" x14ac:dyDescent="0.2">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="741" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A741" t="s">
         <v>51</v>
       </c>
@@ -13957,9 +14012,9 @@
         <v>52</v>
       </c>
     </row>
-    <row r="742" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A742" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B742">
         <v>1.1407711613050422E-5</v>
@@ -13974,10 +14029,10 @@
         <v>78</v>
       </c>
       <c r="H742" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="743" spans="1:8" x14ac:dyDescent="0.2">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="743" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A743" t="s">
         <v>190</v>
       </c>
@@ -13994,10 +14049,10 @@
         <v>78</v>
       </c>
       <c r="H743" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="744" spans="1:8" x14ac:dyDescent="0.2">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="744" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A744" t="s">
         <v>76</v>
       </c>
@@ -14014,10 +14069,10 @@
         <v>78</v>
       </c>
       <c r="H744" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="745" spans="1:8" x14ac:dyDescent="0.2">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="745" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A745" t="s">
         <v>231</v>
       </c>
@@ -14035,13 +14090,13 @@
         <v>77</v>
       </c>
       <c r="G745" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H745" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="746" spans="1:8" x14ac:dyDescent="0.2">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="746" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A746" t="s">
         <v>51</v>
       </c>
@@ -14062,7 +14117,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="747" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A747" t="s">
         <v>100</v>
       </c>
@@ -14083,7 +14138,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H747" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:H747" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="market for silicon tetrachloride"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
